--- a/20250812_Finance/01_source/CompanyABC43_working file_2024.xlsx
+++ b/20250812_Finance/01_source/CompanyABC43_working file_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\AI_Power_Studio\20250812_Finance\01_source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/i0515899/Documents/Git/AI_Power_Studio/20250812_Finance/01_source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78744E4D-2B48-4085-879F-5A211ACE29E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967C7A5D-AA64-7F4F-BFD9-1D61081C37B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="28800" windowHeight="15370" xr2:uid="{0B87AC33-27B1-430C-9C5A-E0A52C6C2ED1}"/>
+    <workbookView xWindow="-4000" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{0B87AC33-27B1-430C-9C5A-E0A52C6C2ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5736,8 +5736,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="#,##0;[Red]\-#,##0;&quot;－&quot;"/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="#,##0;[Red]\-#,##0;&quot;－&quot;"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -5762,7 +5762,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5776,7 +5776,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -5793,7 +5793,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5806,14 +5806,14 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -5831,21 +5831,21 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5853,7 +5853,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5868,7 +5868,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5967,19 +5967,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -6085,39 +6085,39 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="3" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="3" borderId="0" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="15" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
+    <cellStyle name="Comma" xfId="7" builtinId="3"/>
     <cellStyle name="Comma 3" xfId="5" xr:uid="{22D36193-F3AB-42F3-A0B4-7A8CF43FF397}"/>
     <cellStyle name="Comma 4 2" xfId="1" xr:uid="{C3D3FBF7-FC4A-43C2-BBD1-F64AE10C5382}"/>
-    <cellStyle name="標準 3" xfId="2" xr:uid="{3B835E92-BDDB-4760-8570-13D6F2878744}"/>
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔 4" xfId="4" xr:uid="{5F1A85CE-97A1-4F3A-A26E-0F19C8567938}"/>
     <cellStyle name="常规 2 3" xfId="3" xr:uid="{3993C957-A637-44F6-A2BD-3AC7FC4F5359}"/>
     <cellStyle name="常规 3 2" xfId="6" xr:uid="{CEA88AB1-953D-4951-B9CC-54A542B0E4DA}"/>
-    <cellStyle name="千位分隔" xfId="7" builtinId="3"/>
-    <cellStyle name="千位分隔 4" xfId="4" xr:uid="{5F1A85CE-97A1-4F3A-A26E-0F19C8567938}"/>
+    <cellStyle name="標準 3" xfId="2" xr:uid="{3B835E92-BDDB-4760-8570-13D6F2878744}"/>
   </cellStyles>
   <dxfs count="39">
     <dxf>
@@ -6340,6 +6340,9 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
@@ -6347,9 +6350,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
@@ -6816,7 +6816,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B1ECD56-B8D6-4652-884D-D3FC88BF5437}">
   <dimension ref="A1:L2206"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14" outlineLevelCol="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="24" style="14" customWidth="1"/>
     <col min="2" max="2" width="24" style="5" customWidth="1" outlineLevel="1"/>
@@ -6824,10 +6824,10 @@
     <col min="4" max="8" width="24" style="5" customWidth="1"/>
     <col min="9" max="9" width="24" style="46" customWidth="1"/>
     <col min="10" max="12" width="24" style="47" customWidth="1"/>
-    <col min="13" max="16384" width="9.08984375" style="5"/>
+    <col min="13" max="16384" width="9.1640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="78.650000000000006" customHeight="1">
+    <row r="1" spans="1:12" ht="78.75" customHeight="1">
       <c r="A1" s="37" t="s">
         <v>68</v>
       </c>
@@ -6865,7 +6865,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="6" customFormat="1" ht="12.65" customHeight="1">
+    <row r="2" spans="1:12" s="6" customFormat="1" ht="12.75" customHeight="1">
       <c r="A2" s="16">
         <v>11111001</v>
       </c>
@@ -8189,7 +8189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" s="6" customFormat="1" ht="12.65" customHeight="1">
+    <row r="51" spans="1:12" s="6" customFormat="1" ht="12.75" customHeight="1">
       <c r="A51" s="16">
         <v>19130001</v>
       </c>
@@ -10571,7 +10571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:12" s="6" customFormat="1" ht="14.4" customHeight="1">
+    <row r="139" spans="1:12" s="6" customFormat="1" ht="14.5" customHeight="1">
       <c r="A139" s="16">
         <v>13323101</v>
       </c>
@@ -15404,7 +15404,7 @@
         <v>-2956.0295038253826</v>
       </c>
     </row>
-    <row r="318" spans="1:12" s="6" customFormat="1" ht="12.65" customHeight="1">
+    <row r="318" spans="1:12" s="6" customFormat="1" ht="12.75" customHeight="1">
       <c r="A318" s="16">
         <v>21348205</v>
       </c>
@@ -17807,7 +17807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:12" s="6" customFormat="1" ht="12.65" customHeight="1">
+    <row r="407" spans="1:12" s="6" customFormat="1" ht="12.75" customHeight="1">
       <c r="A407" s="27" t="s">
         <v>100</v>
       </c>
@@ -25606,7 +25606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="689" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="689" spans="1:12" s="6" customFormat="1">
       <c r="A689" s="27" t="s">
         <v>382</v>
       </c>
@@ -32606,7 +32606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="939" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="939" spans="1:12" s="6" customFormat="1">
       <c r="A939" s="27" t="s">
         <v>632</v>
       </c>
@@ -43317,7 +43317,7 @@
         <v>-0.18129950495049507</v>
       </c>
     </row>
-    <row r="1322" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1322" spans="1:12" s="6" customFormat="1">
       <c r="A1322" s="27" t="s">
         <v>1010</v>
       </c>
@@ -51493,7 +51493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1614" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1614" spans="1:12" s="6" customFormat="1">
       <c r="A1614" s="27" t="s">
         <v>1302</v>
       </c>
@@ -56869,7 +56869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1806" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1806" spans="1:12" s="6" customFormat="1">
       <c r="A1806" s="27" t="s">
         <v>1494</v>
       </c>
@@ -60787,7 +60787,7 @@
         <v>657.79081795679565</v>
       </c>
     </row>
-    <row r="1946" spans="1:12" s="6" customFormat="1" ht="14.4" customHeight="1">
+    <row r="1946" spans="1:12" s="6" customFormat="1" ht="14.5" customHeight="1">
       <c r="A1946" s="27" t="s">
         <v>1632</v>
       </c>
@@ -61207,7 +61207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1961" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1961" spans="1:12" s="6" customFormat="1">
       <c r="A1961" s="27" t="s">
         <v>1647</v>
       </c>
@@ -61235,7 +61235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1962" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1962" spans="1:12" s="6" customFormat="1">
       <c r="A1962" s="27" t="s">
         <v>1648</v>
       </c>
@@ -61263,7 +61263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1963" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1963" spans="1:12" s="6" customFormat="1">
       <c r="A1963" s="27" t="s">
         <v>1649</v>
       </c>
@@ -61291,7 +61291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1964" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1964" spans="1:12" s="6" customFormat="1">
       <c r="A1964" s="27" t="s">
         <v>1650</v>
       </c>
@@ -61319,7 +61319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1965" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1965" spans="1:12" s="6" customFormat="1">
       <c r="A1965" s="27" t="s">
         <v>1651</v>
       </c>
@@ -61347,7 +61347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1966" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1966" spans="1:12" s="6" customFormat="1">
       <c r="A1966" s="27" t="s">
         <v>1652</v>
       </c>
@@ -61375,7 +61375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1967" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1967" spans="1:12" s="6" customFormat="1">
       <c r="A1967" s="27" t="s">
         <v>1653</v>
       </c>
@@ -61403,7 +61403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1968" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1968" spans="1:12" s="6" customFormat="1">
       <c r="A1968" s="27" t="s">
         <v>1654</v>
       </c>
@@ -61431,7 +61431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1969" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1969" spans="1:12" s="6" customFormat="1">
       <c r="A1969" s="27" t="s">
         <v>1655</v>
       </c>
@@ -61459,7 +61459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1970" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1970" spans="1:12" s="6" customFormat="1">
       <c r="A1970" s="27" t="s">
         <v>1656</v>
       </c>
@@ -61487,7 +61487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1971" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1971" spans="1:12" s="6" customFormat="1">
       <c r="A1971" s="27" t="s">
         <v>1657</v>
       </c>
@@ -61515,7 +61515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1972" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1972" spans="1:12" s="6" customFormat="1">
       <c r="A1972" s="27" t="s">
         <v>1658</v>
       </c>
@@ -61543,7 +61543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1973" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1973" spans="1:12" s="6" customFormat="1">
       <c r="A1973" s="27" t="s">
         <v>1659</v>
       </c>
@@ -61571,7 +61571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1974" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1974" spans="1:12" s="6" customFormat="1">
       <c r="A1974" s="27" t="s">
         <v>1660</v>
       </c>
@@ -61599,7 +61599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1975" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1975" spans="1:12" s="6" customFormat="1">
       <c r="A1975" s="27" t="s">
         <v>1661</v>
       </c>
@@ -61627,7 +61627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1976" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1976" spans="1:12" s="6" customFormat="1">
       <c r="A1976" s="27" t="s">
         <v>1662</v>
       </c>
@@ -61655,7 +61655,7 @@
         <v>0.357755400540054</v>
       </c>
     </row>
-    <row r="1977" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1977" spans="1:12" s="6" customFormat="1">
       <c r="A1977" s="27" t="s">
         <v>1663</v>
       </c>
@@ -61683,7 +61683,7 @@
         <v>-78.428518226822689</v>
       </c>
     </row>
-    <row r="1978" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1978" spans="1:12" s="6" customFormat="1">
       <c r="A1978" s="27" t="s">
         <v>1664</v>
       </c>
@@ -61711,7 +61711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1979" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1979" spans="1:12" s="6" customFormat="1">
       <c r="A1979" s="27" t="s">
         <v>1665</v>
       </c>
@@ -61739,7 +61739,7 @@
         <v>129.45756188118813</v>
       </c>
     </row>
-    <row r="1980" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1980" spans="1:12" s="6" customFormat="1">
       <c r="A1980" s="27" t="s">
         <v>1666</v>
       </c>
@@ -61767,7 +61767,7 @@
         <v>-7.1953926642663379</v>
       </c>
     </row>
-    <row r="1981" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1981" spans="1:12" s="6" customFormat="1">
       <c r="A1981" s="27" t="s">
         <v>1667</v>
       </c>
@@ -61795,7 +61795,7 @@
         <v>-75.945094509450939</v>
       </c>
     </row>
-    <row r="1982" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1982" spans="1:12" s="6" customFormat="1">
       <c r="A1982" s="27" t="s">
         <v>1668</v>
       </c>
@@ -61823,7 +61823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1983" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1983" spans="1:12" s="6" customFormat="1">
       <c r="A1983" s="27" t="s">
         <v>1669</v>
       </c>
@@ -61851,7 +61851,7 @@
         <v>2.4901395139513953</v>
       </c>
     </row>
-    <row r="1984" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1984" spans="1:12" s="6" customFormat="1">
       <c r="A1984" s="27" t="s">
         <v>1670</v>
       </c>
@@ -61879,7 +61879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1985" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1985" spans="1:12" s="6" customFormat="1">
       <c r="A1985" s="27" t="s">
         <v>1671</v>
       </c>
@@ -61907,7 +61907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1986" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1986" spans="1:12" s="6" customFormat="1">
       <c r="A1986" s="27" t="s">
         <v>1672</v>
       </c>
@@ -61935,7 +61935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1987" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1987" spans="1:12" s="6" customFormat="1">
       <c r="A1987" s="27" t="s">
         <v>1673</v>
       </c>
@@ -61963,7 +61963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1988" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1988" spans="1:12" s="6" customFormat="1">
       <c r="A1988" s="27" t="s">
         <v>1674</v>
       </c>
@@ -61991,7 +61991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1989" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1989" spans="1:12" s="6" customFormat="1">
       <c r="A1989" s="27" t="s">
         <v>1675</v>
       </c>
@@ -62019,7 +62019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1990" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1990" spans="1:12" s="6" customFormat="1">
       <c r="A1990" s="27" t="s">
         <v>1676</v>
       </c>
@@ -62047,7 +62047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1991" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1991" spans="1:12" s="6" customFormat="1">
       <c r="A1991" s="27" t="s">
         <v>1677</v>
       </c>
@@ -62075,7 +62075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1992" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1992" spans="1:12" s="6" customFormat="1">
       <c r="A1992" s="27" t="s">
         <v>1678</v>
       </c>
@@ -62103,7 +62103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1993" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1993" spans="1:12" s="6" customFormat="1">
       <c r="A1993" s="27" t="s">
         <v>1679</v>
       </c>
@@ -62131,7 +62131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1994" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1994" spans="1:12" s="6" customFormat="1">
       <c r="A1994" s="27" t="s">
         <v>1680</v>
       </c>
@@ -62159,7 +62159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1995" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1995" spans="1:12" s="6" customFormat="1">
       <c r="A1995" s="27" t="s">
         <v>1681</v>
       </c>
@@ -62187,7 +62187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1996" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1996" spans="1:12" s="6" customFormat="1">
       <c r="A1996" s="27" t="s">
         <v>1682</v>
       </c>
@@ -62215,7 +62215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1997" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1997" spans="1:12" s="6" customFormat="1">
       <c r="A1997" s="27" t="s">
         <v>1683</v>
       </c>
@@ -62243,7 +62243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1998" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1998" spans="1:12" s="6" customFormat="1">
       <c r="A1998" s="27" t="s">
         <v>1684</v>
       </c>
@@ -62271,7 +62271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1999" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="1999" spans="1:12" s="6" customFormat="1">
       <c r="A1999" s="27" t="s">
         <v>1685</v>
       </c>
@@ -62299,7 +62299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2000" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2000" spans="1:12" s="6" customFormat="1">
       <c r="A2000" s="27" t="s">
         <v>1686</v>
       </c>
@@ -62327,7 +62327,7 @@
         <v>0.50508775877587764</v>
       </c>
     </row>
-    <row r="2001" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2001" spans="1:12" s="6" customFormat="1">
       <c r="A2001" s="27" t="s">
         <v>1687</v>
       </c>
@@ -62355,7 +62355,7 @@
         <v>-709.30465909090901</v>
       </c>
     </row>
-    <row r="2002" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2002" spans="1:12" s="6" customFormat="1">
       <c r="A2002" s="27" t="s">
         <v>1688</v>
       </c>
@@ -62383,7 +62383,7 @@
         <v>3.9701473897389739</v>
       </c>
     </row>
-    <row r="2003" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2003" spans="1:12" s="6" customFormat="1">
       <c r="A2003" s="27" t="s">
         <v>1689</v>
       </c>
@@ -62411,7 +62411,7 @@
         <v>-170.47424954995498</v>
       </c>
     </row>
-    <row r="2004" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2004" spans="1:12" s="6" customFormat="1">
       <c r="A2004" s="27" t="s">
         <v>1690</v>
       </c>
@@ -62439,7 +62439,7 @@
         <v>20.761109360936093</v>
       </c>
     </row>
-    <row r="2005" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2005" spans="1:12" s="6" customFormat="1">
       <c r="A2005" s="27" t="s">
         <v>1691</v>
       </c>
@@ -62467,7 +62467,7 @@
         <v>-661.56615661566161</v>
       </c>
     </row>
-    <row r="2006" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2006" spans="1:12" s="6" customFormat="1">
       <c r="A2006" s="27" t="s">
         <v>1692</v>
       </c>
@@ -62495,7 +62495,7 @@
         <v>75.159663591359148</v>
       </c>
     </row>
-    <row r="2007" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2007" spans="1:12" s="6" customFormat="1">
       <c r="A2007" s="27" t="s">
         <v>1693</v>
       </c>
@@ -62523,7 +62523,7 @@
         <v>103.09839108910892</v>
       </c>
     </row>
-    <row r="2008" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2008" spans="1:12" s="6" customFormat="1">
       <c r="A2008" s="31" t="s">
         <v>1694</v>
       </c>
@@ -62550,7 +62550,7 @@
         <v>40.004153915391541</v>
       </c>
     </row>
-    <row r="2009" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2009" spans="1:12" s="6" customFormat="1">
       <c r="A2009" s="31" t="s">
         <v>1695</v>
       </c>
@@ -62577,7 +62577,7 @@
         <v>552.9214378937894</v>
       </c>
     </row>
-    <row r="2010" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2010" spans="1:12" s="6" customFormat="1">
       <c r="A2010" s="31" t="s">
         <v>1696</v>
       </c>
@@ -62604,7 +62604,7 @@
         <v>-45.093894014401442</v>
       </c>
     </row>
-    <row r="2011" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2011" spans="1:12" s="6" customFormat="1">
       <c r="A2011" s="31" t="s">
         <v>1697</v>
       </c>
@@ -62631,7 +62631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2012" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2012" spans="1:12" s="6" customFormat="1">
       <c r="A2012" s="31" t="s">
         <v>1698</v>
       </c>
@@ -62658,7 +62658,7 @@
         <v>630.4063692619261</v>
       </c>
     </row>
-    <row r="2013" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2013" spans="1:12" s="6" customFormat="1">
       <c r="A2013" s="31" t="s">
         <v>1699</v>
       </c>
@@ -62685,7 +62685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2014" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2014" spans="1:12" s="6" customFormat="1">
       <c r="A2014" s="31" t="s">
         <v>1700</v>
       </c>
@@ -62712,7 +62712,7 @@
         <v>-15.220969846984699</v>
       </c>
     </row>
-    <row r="2015" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2015" spans="1:12" s="6" customFormat="1">
       <c r="A2015" s="31" t="s">
         <v>1701</v>
       </c>
@@ -62793,7 +62793,7 @@
         <v>41615.475524302426</v>
       </c>
     </row>
-    <row r="2018" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2018" spans="1:12" s="6" customFormat="1">
       <c r="A2018" s="31" t="s">
         <v>772</v>
       </c>
@@ -62820,7 +62820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2019" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2019" spans="1:12" s="6" customFormat="1">
       <c r="A2019" s="31" t="s">
         <v>81</v>
       </c>
@@ -62847,7 +62847,7 @@
         <v>-1.5402790279027902E-3</v>
       </c>
     </row>
-    <row r="2020" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2020" spans="1:12" s="6" customFormat="1">
       <c r="A2020" s="31" t="s">
         <v>1703</v>
       </c>
@@ -62874,7 +62874,7 @@
         <v>10.812445994599463</v>
       </c>
     </row>
-    <row r="2021" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2021" spans="1:12" s="6" customFormat="1">
       <c r="A2021" s="31" t="s">
         <v>1704</v>
       </c>
@@ -62901,7 +62901,7 @@
         <v>-209.98006075607563</v>
       </c>
     </row>
-    <row r="2022" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2022" spans="1:12" s="6" customFormat="1">
       <c r="A2022" s="31" t="s">
         <v>1705</v>
       </c>
@@ -62928,7 +62928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2023" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2023" spans="1:12" s="6" customFormat="1">
       <c r="A2023" s="31" t="s">
         <v>1706</v>
       </c>
@@ -62955,7 +62955,7 @@
         <v>46.124156165616562</v>
       </c>
     </row>
-    <row r="2024" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2024" spans="1:12" s="6" customFormat="1">
       <c r="A2024" s="31" t="s">
         <v>1707</v>
       </c>
@@ -62982,7 +62982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2025" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2025" spans="1:12" s="6" customFormat="1">
       <c r="A2025" s="31" t="s">
         <v>1708</v>
       </c>
@@ -63009,7 +63009,7 @@
         <v>-46.124156165616526</v>
       </c>
     </row>
-    <row r="2026" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2026" spans="1:12" s="6" customFormat="1">
       <c r="A2026" s="31" t="s">
         <v>1709</v>
       </c>
@@ -63036,7 +63036,7 @@
         <v>29.667538253825384</v>
       </c>
     </row>
-    <row r="2027" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2027" spans="1:12" s="6" customFormat="1">
       <c r="A2027" s="31" t="s">
         <v>1710</v>
       </c>
@@ -63063,7 +63063,7 @@
         <v>-9.3956784428442841</v>
       </c>
     </row>
-    <row r="2028" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2028" spans="1:12" s="6" customFormat="1">
       <c r="A2028" s="31" t="s">
         <v>1711</v>
       </c>
@@ -63090,7 +63090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2029" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2029" spans="1:12" s="6" customFormat="1">
       <c r="A2029" s="31" t="s">
         <v>1712</v>
       </c>
@@ -63117,7 +63117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2030" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2030" spans="1:12" s="6" customFormat="1">
       <c r="A2030" s="31" t="s">
         <v>1713</v>
       </c>
@@ -63144,7 +63144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2031" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2031" spans="1:12" s="6" customFormat="1">
       <c r="A2031" s="31" t="s">
         <v>1714</v>
       </c>
@@ -63171,7 +63171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2032" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2032" spans="1:12" s="6" customFormat="1">
       <c r="A2032" s="31" t="s">
         <v>1715</v>
       </c>
@@ -63198,7 +63198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2033" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2033" spans="1:12" s="6" customFormat="1">
       <c r="A2033" s="31" t="s">
         <v>1716</v>
       </c>
@@ -63225,7 +63225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2034" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2034" spans="1:12" s="6" customFormat="1">
       <c r="A2034" s="31" t="s">
         <v>1717</v>
       </c>
@@ -63252,7 +63252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2035" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2035" spans="1:12" s="6" customFormat="1">
       <c r="A2035" s="31" t="s">
         <v>1718</v>
       </c>
@@ -63279,7 +63279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2036" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2036" spans="1:12" s="6" customFormat="1">
       <c r="A2036" s="31" t="s">
         <v>1719</v>
       </c>
@@ -63306,7 +63306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2037" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2037" spans="1:12" s="6" customFormat="1">
       <c r="A2037" s="31" t="s">
         <v>1720</v>
       </c>
@@ -63333,7 +63333,7 @@
         <v>796.42076620162027</v>
       </c>
     </row>
-    <row r="2038" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2038" spans="1:12" s="6" customFormat="1">
       <c r="A2038" s="31" t="s">
         <v>1721</v>
       </c>
@@ -63360,7 +63360,7 @@
         <v>368.44239423942395</v>
       </c>
     </row>
-    <row r="2039" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2039" spans="1:12" s="6" customFormat="1">
       <c r="A2039" s="31" t="s">
         <v>1722</v>
       </c>
@@ -63387,7 +63387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2040" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2040" spans="1:12" s="6" customFormat="1">
       <c r="A2040" s="31" t="s">
         <v>1723</v>
       </c>
@@ -63414,7 +63414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2041" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2041" spans="1:12" s="6" customFormat="1">
       <c r="A2041" s="31" t="s">
         <v>1724</v>
       </c>
@@ -63441,7 +63441,7 @@
         <v>27111.649785103509</v>
       </c>
     </row>
-    <row r="2042" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2042" spans="1:12" s="6" customFormat="1">
       <c r="A2042" s="31" t="s">
         <v>1725</v>
       </c>
@@ -63468,7 +63468,7 @@
         <v>37.691269126912694</v>
       </c>
     </row>
-    <row r="2043" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2043" spans="1:12" s="6" customFormat="1">
       <c r="A2043" s="31" t="s">
         <v>1726</v>
       </c>
@@ -63495,7 +63495,7 @@
         <v>21447.128748874879</v>
       </c>
     </row>
-    <row r="2044" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2044" spans="1:12" s="6" customFormat="1">
       <c r="A2044" s="31" t="s">
         <v>1727</v>
       </c>
@@ -63522,7 +63522,7 @@
         <v>-27488.515110261029</v>
       </c>
     </row>
-    <row r="2045" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2045" spans="1:12" s="6" customFormat="1">
       <c r="A2045" s="31" t="s">
         <v>1728</v>
       </c>
@@ -63549,7 +63549,7 @@
         <v>274.60264963996406</v>
       </c>
     </row>
-    <row r="2046" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2046" spans="1:12" s="6" customFormat="1">
       <c r="A2046" s="31" t="s">
         <v>1729</v>
       </c>
@@ -63576,7 +63576,7 @@
         <v>2251.337173717372</v>
       </c>
     </row>
-    <row r="2047" spans="1:12" ht="14.5">
+    <row r="2047" spans="1:12">
       <c r="A2047" s="31" t="s">
         <v>1730</v>
       </c>
@@ -63603,7 +63603,7 @@
         <v>1777.4955760576058</v>
       </c>
     </row>
-    <row r="2048" spans="1:12" ht="14.5">
+    <row r="2048" spans="1:12">
       <c r="A2048" s="27" t="s">
         <v>1731</v>
       </c>
@@ -63631,7 +63631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2049" spans="1:12" ht="14.5">
+    <row r="2049" spans="1:12">
       <c r="A2049" s="27" t="s">
         <v>1732</v>
       </c>
@@ -63659,7 +63659,7 @@
         <v>-1083.1794723222322</v>
       </c>
     </row>
-    <row r="2050" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2050" spans="1:12" s="6" customFormat="1">
       <c r="A2050" s="27" t="s">
         <v>1733</v>
       </c>
@@ -63687,7 +63687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2051" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2051" spans="1:12" s="6" customFormat="1">
       <c r="A2051" s="27" t="s">
         <v>1734</v>
       </c>
@@ -63715,7 +63715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2052" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2052" spans="1:12" s="6" customFormat="1">
       <c r="A2052" s="27" t="s">
         <v>1735</v>
       </c>
@@ -63743,7 +63743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2053" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2053" spans="1:12" s="6" customFormat="1">
       <c r="A2053" s="27" t="s">
         <v>1736</v>
       </c>
@@ -63771,7 +63771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2054" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2054" spans="1:12" s="6" customFormat="1">
       <c r="A2054" s="27" t="s">
         <v>1737</v>
       </c>
@@ -63799,7 +63799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2055" spans="1:12" s="6" customFormat="1" ht="14.5">
+    <row r="2055" spans="1:12" s="6" customFormat="1">
       <c r="A2055" s="31" t="s">
         <v>1738</v>
       </c>
@@ -63826,7 +63826,7 @@
         <v>589.75167754275424</v>
       </c>
     </row>
-    <row r="2056" spans="1:12" ht="14.5">
+    <row r="2056" spans="1:12">
       <c r="A2056" s="27" t="s">
         <v>1739</v>
       </c>
@@ -63854,7 +63854,7 @@
         <v>87.320463546354645</v>
       </c>
     </row>
-    <row r="2057" spans="1:12" ht="14.5">
+    <row r="2057" spans="1:12">
       <c r="A2057" s="27" t="s">
         <v>1740</v>
       </c>
@@ -63882,7 +63882,7 @@
         <v>3.013665616561656</v>
       </c>
     </row>
-    <row r="2058" spans="1:12" ht="14.5">
+    <row r="2058" spans="1:12">
       <c r="A2058" s="27" t="s">
         <v>1741</v>
       </c>
@@ -63910,7 +63910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2059" spans="1:12" ht="14.5">
+    <row r="2059" spans="1:12">
       <c r="A2059" s="27" t="s">
         <v>1742</v>
       </c>
@@ -63938,7 +63938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2060" spans="1:12" ht="14.5">
+    <row r="2060" spans="1:12">
       <c r="A2060" s="27" t="s">
         <v>1743</v>
       </c>
@@ -63966,7 +63966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2061" spans="1:12" ht="14.5">
+    <row r="2061" spans="1:12">
       <c r="A2061" s="27" t="s">
         <v>1744</v>
       </c>
@@ -63994,7 +63994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2062" spans="1:12" ht="14.5">
+    <row r="2062" spans="1:12">
       <c r="A2062" s="27" t="s">
         <v>1745</v>
       </c>
@@ -64022,7 +64022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2063" spans="1:12" ht="14.5">
+    <row r="2063" spans="1:12">
       <c r="A2063" s="27" t="s">
         <v>1746</v>
       </c>
@@ -64050,7 +64050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2064" spans="1:12" ht="14.5">
+    <row r="2064" spans="1:12">
       <c r="A2064" s="27" t="s">
         <v>1747</v>
       </c>
@@ -64078,7 +64078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2065" spans="1:12" ht="14.5">
+    <row r="2065" spans="1:12">
       <c r="A2065" s="27" t="s">
         <v>1748</v>
       </c>
@@ -64106,7 +64106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2066" spans="1:12" ht="14.5">
+    <row r="2066" spans="1:12">
       <c r="A2066" s="27" t="s">
         <v>1749</v>
       </c>
@@ -64134,7 +64134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2067" spans="1:12" ht="14.5">
+    <row r="2067" spans="1:12">
       <c r="A2067" s="27" t="s">
         <v>1750</v>
       </c>
@@ -64162,7 +64162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2068" spans="1:12" ht="14.5">
+    <row r="2068" spans="1:12">
       <c r="A2068" s="27" t="s">
         <v>1751</v>
       </c>
@@ -64190,7 +64190,7 @@
         <v>5.3509169666966692</v>
       </c>
     </row>
-    <row r="2069" spans="1:12" ht="14.5">
+    <row r="2069" spans="1:12">
       <c r="A2069" s="27" t="s">
         <v>1752</v>
       </c>
@@ -64218,7 +64218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2070" spans="1:12" ht="14.5">
+    <row r="2070" spans="1:12">
       <c r="A2070" s="27" t="s">
         <v>1753</v>
       </c>
@@ -64246,7 +64246,7 @@
         <v>661.53231660666074</v>
       </c>
     </row>
-    <row r="2071" spans="1:12" ht="14.5">
+    <row r="2071" spans="1:12">
       <c r="A2071" s="27" t="s">
         <v>1754</v>
       </c>
@@ -64274,7 +64274,7 @@
         <v>-8.5452711521152249</v>
       </c>
     </row>
-    <row r="2072" spans="1:12" ht="14.5">
+    <row r="2072" spans="1:12">
       <c r="A2072" s="27" t="s">
         <v>1755</v>
       </c>
@@ -64302,7 +64302,7 @@
         <v>298.67816156615663</v>
       </c>
     </row>
-    <row r="2073" spans="1:12" ht="14.5">
+    <row r="2073" spans="1:12">
       <c r="A2073" s="27" t="s">
         <v>1756</v>
       </c>
@@ -64330,7 +64330,7 @@
         <v>148.50724459945994</v>
       </c>
     </row>
-    <row r="2074" spans="1:12" ht="14.5">
+    <row r="2074" spans="1:12">
       <c r="A2074" s="27" t="s">
         <v>1757</v>
       </c>
@@ -64358,7 +64358,7 @@
         <v>-36.09523852385238</v>
       </c>
     </row>
-    <row r="2075" spans="1:12" ht="14.5">
+    <row r="2075" spans="1:12">
       <c r="A2075" s="27" t="s">
         <v>1758</v>
       </c>
@@ -64386,7 +64386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2076" spans="1:12" ht="14.5">
+    <row r="2076" spans="1:12">
       <c r="A2076" s="27" t="s">
         <v>1759</v>
       </c>
@@ -64414,7 +64414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2077" spans="1:12" ht="14.5">
+    <row r="2077" spans="1:12">
       <c r="A2077" s="27" t="s">
         <v>1760</v>
       </c>
@@ -64442,7 +64442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2078" spans="1:12" ht="14.5">
+    <row r="2078" spans="1:12">
       <c r="A2078" s="27" t="s">
         <v>1761</v>
       </c>
@@ -64470,7 +64470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2079" spans="1:12" ht="14.5">
+    <row r="2079" spans="1:12">
       <c r="A2079" s="27" t="s">
         <v>1762</v>
       </c>
@@ -64498,7 +64498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2080" spans="1:12" ht="14.5">
+    <row r="2080" spans="1:12">
       <c r="A2080" s="27" t="s">
         <v>1763</v>
       </c>
@@ -64526,7 +64526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2081" spans="1:12" ht="14.5">
+    <row r="2081" spans="1:12">
       <c r="A2081" s="27" t="s">
         <v>1764</v>
       </c>
@@ -64554,7 +64554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2082" spans="1:12" ht="14.5">
+    <row r="2082" spans="1:12">
       <c r="A2082" s="27" t="s">
         <v>1765</v>
       </c>
@@ -64582,7 +64582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2083" spans="1:12" ht="14.5">
+    <row r="2083" spans="1:12">
       <c r="A2083" s="27" t="s">
         <v>1766</v>
       </c>
@@ -64610,7 +64610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2084" spans="1:12" ht="14.5">
+    <row r="2084" spans="1:12">
       <c r="A2084" s="27" t="s">
         <v>1767</v>
       </c>
@@ -64638,7 +64638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2085" spans="1:12" ht="14.5">
+    <row r="2085" spans="1:12">
       <c r="A2085" s="27" t="s">
         <v>1768</v>
       </c>
@@ -64666,7 +64666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2086" spans="1:12" ht="14.5">
+    <row r="2086" spans="1:12">
       <c r="A2086" s="27" t="s">
         <v>1769</v>
       </c>
@@ -64694,7 +64694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2087" spans="1:12" ht="14.5">
+    <row r="2087" spans="1:12">
       <c r="A2087" s="27" t="s">
         <v>1770</v>
       </c>
@@ -64722,7 +64722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2088" spans="1:12" ht="14.5">
+    <row r="2088" spans="1:12">
       <c r="A2088" s="27" t="s">
         <v>1771</v>
       </c>
@@ -64750,7 +64750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2089" spans="1:12" ht="14.5">
+    <row r="2089" spans="1:12">
       <c r="A2089" s="27" t="s">
         <v>1772</v>
       </c>
@@ -64778,7 +64778,7 @@
         <v>54.00832583258326</v>
       </c>
     </row>
-    <row r="2090" spans="1:12" ht="14.5">
+    <row r="2090" spans="1:12">
       <c r="A2090" s="27" t="s">
         <v>1773</v>
       </c>
@@ -64806,7 +64806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2091" spans="1:12" ht="14.5">
+    <row r="2091" spans="1:12">
       <c r="A2091" s="27" t="s">
         <v>1774</v>
       </c>
@@ -64834,7 +64834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2092" spans="1:12" ht="14.5">
+    <row r="2092" spans="1:12">
       <c r="A2092" s="27" t="s">
         <v>1775</v>
       </c>
@@ -64862,7 +64862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2093" spans="1:12" ht="14.5">
+    <row r="2093" spans="1:12">
       <c r="A2093" s="27" t="s">
         <v>1776</v>
       </c>
@@ -64890,7 +64890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2094" spans="1:12" ht="14.5">
+    <row r="2094" spans="1:12">
       <c r="A2094" s="27" t="s">
         <v>1777</v>
       </c>
@@ -64918,7 +64918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2095" spans="1:12" ht="14.5">
+    <row r="2095" spans="1:12">
       <c r="A2095" s="27" t="s">
         <v>1778</v>
       </c>
@@ -64946,7 +64946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2096" spans="1:12" ht="14.5">
+    <row r="2096" spans="1:12">
       <c r="A2096" s="27" t="s">
         <v>1779</v>
       </c>
@@ -64974,7 +64974,7 @@
         <v>2.4036903690369038</v>
       </c>
     </row>
-    <row r="2097" spans="1:12" ht="14.5">
+    <row r="2097" spans="1:12">
       <c r="A2097" s="27" t="s">
         <v>1780</v>
       </c>
@@ -65002,7 +65002,7 @@
         <v>2.0831390639063905</v>
       </c>
     </row>
-    <row r="2098" spans="1:12" ht="14.5">
+    <row r="2098" spans="1:12">
       <c r="A2098" s="27" t="s">
         <v>1781</v>
       </c>
@@ -65030,7 +65030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2099" spans="1:12" ht="14.5">
+    <row r="2099" spans="1:12">
       <c r="A2099" s="27" t="s">
         <v>1782</v>
       </c>
@@ -65058,7 +65058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2100" spans="1:12" ht="14.5">
+    <row r="2100" spans="1:12">
       <c r="A2100" s="27" t="s">
         <v>1783</v>
       </c>
@@ -65086,7 +65086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2101" spans="1:12" ht="14.5">
+    <row r="2101" spans="1:12">
       <c r="A2101" s="27" t="s">
         <v>1784</v>
       </c>
@@ -65114,7 +65114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2102" spans="1:12" ht="14.5">
+    <row r="2102" spans="1:12">
       <c r="A2102" s="27" t="s">
         <v>1785</v>
       </c>
@@ -65142,7 +65142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2103" spans="1:12" ht="14.5">
+    <row r="2103" spans="1:12">
       <c r="A2103" s="27" t="s">
         <v>1786</v>
       </c>
@@ -65170,7 +65170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2104" spans="1:12" ht="14.5">
+    <row r="2104" spans="1:12">
       <c r="A2104" s="27" t="s">
         <v>1787</v>
       </c>
@@ -65198,7 +65198,7 @@
         <v>0.97036341134113413</v>
       </c>
     </row>
-    <row r="2105" spans="1:12" ht="14.5">
+    <row r="2105" spans="1:12">
       <c r="A2105" s="27" t="s">
         <v>1788</v>
       </c>
@@ -65226,7 +65226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2106" spans="1:12" ht="14.5">
+    <row r="2106" spans="1:12">
       <c r="A2106" s="27" t="s">
         <v>1789</v>
       </c>
@@ -65254,7 +65254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2107" spans="1:12" ht="14.5">
+    <row r="2107" spans="1:12">
       <c r="A2107" s="27" t="s">
         <v>1790</v>
       </c>
@@ -65282,7 +65282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2108" spans="1:12" ht="14.5">
+    <row r="2108" spans="1:12">
       <c r="A2108" s="27" t="s">
         <v>1791</v>
       </c>
@@ -65310,7 +65310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2109" spans="1:12" ht="14.5">
+    <row r="2109" spans="1:12">
       <c r="A2109" s="27" t="s">
         <v>1792</v>
       </c>
@@ -65338,7 +65338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2110" spans="1:12" ht="14.5">
+    <row r="2110" spans="1:12">
       <c r="A2110" s="27" t="s">
         <v>1793</v>
       </c>
@@ -65366,7 +65366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2111" spans="1:12" ht="14.5">
+    <row r="2111" spans="1:12">
       <c r="A2111" s="27" t="s">
         <v>1794</v>
       </c>
@@ -65394,7 +65394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2112" spans="1:12" ht="14.5">
+    <row r="2112" spans="1:12">
       <c r="A2112" s="27" t="s">
         <v>1795</v>
       </c>
@@ -65422,7 +65422,7 @@
         <v>6.6865436543654365E-3</v>
       </c>
     </row>
-    <row r="2113" spans="1:12" ht="14.5">
+    <row r="2113" spans="1:12">
       <c r="A2113" s="27" t="s">
         <v>1796</v>
       </c>
@@ -65450,7 +65450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2114" spans="1:12" ht="14.5">
+    <row r="2114" spans="1:12">
       <c r="A2114" s="27" t="s">
         <v>1797</v>
       </c>
@@ -65478,7 +65478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2115" spans="1:12" ht="14.5">
+    <row r="2115" spans="1:12">
       <c r="A2115" s="27" t="s">
         <v>1798</v>
       </c>
@@ -65506,7 +65506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2116" spans="1:12" ht="14.5">
+    <row r="2116" spans="1:12">
       <c r="A2116" s="27" t="s">
         <v>1799</v>
       </c>
@@ -65534,7 +65534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2117" spans="1:12" ht="14.5">
+    <row r="2117" spans="1:12">
       <c r="A2117" s="27" t="s">
         <v>1800</v>
       </c>
@@ -65562,7 +65562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2118" spans="1:12" ht="14.5">
+    <row r="2118" spans="1:12">
       <c r="A2118" s="27" t="s">
         <v>1801</v>
       </c>
@@ -65590,7 +65590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2119" spans="1:12" ht="14.5">
+    <row r="2119" spans="1:12">
       <c r="A2119" s="27" t="s">
         <v>1802</v>
       </c>
@@ -65618,7 +65618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2120" spans="1:12" ht="14.5">
+    <row r="2120" spans="1:12">
       <c r="A2120" s="27" t="s">
         <v>1803</v>
       </c>
@@ -65646,7 +65646,7 @@
         <v>16.973461971197121</v>
       </c>
     </row>
-    <row r="2121" spans="1:12" ht="14.5">
+    <row r="2121" spans="1:12">
       <c r="A2121" s="27" t="s">
         <v>1804</v>
       </c>
@@ -65674,7 +65674,7 @@
         <v>21.266724797479746</v>
       </c>
     </row>
-    <row r="2122" spans="1:12" ht="14.5">
+    <row r="2122" spans="1:12">
       <c r="A2122" s="27" t="s">
         <v>1805</v>
       </c>
@@ -65702,7 +65702,7 @@
         <v>-0.66574594959495947</v>
       </c>
     </row>
-    <row r="2123" spans="1:12" ht="14.5">
+    <row r="2123" spans="1:12">
       <c r="A2123" s="27" t="s">
         <v>1806</v>
       </c>
@@ -65730,7 +65730,7 @@
         <v>7.7994216921692168</v>
       </c>
     </row>
-    <row r="2124" spans="1:12" ht="14.5">
+    <row r="2124" spans="1:12">
       <c r="A2124" s="16">
         <v>11111016</v>
       </c>
@@ -65757,7 +65757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2125" spans="1:12" ht="14.5">
+    <row r="2125" spans="1:12">
       <c r="A2125" s="16">
         <v>19190001</v>
       </c>
@@ -65784,7 +65784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2126" spans="1:12" ht="14.5">
+    <row r="2126" spans="1:12">
       <c r="A2126" s="16">
         <v>11411004</v>
       </c>
@@ -65811,7 +65811,7 @@
         <v>-5015.8923953645362</v>
       </c>
     </row>
-    <row r="2127" spans="1:12" ht="14.5">
+    <row r="2127" spans="1:12">
       <c r="A2127" s="16">
         <v>11413007</v>
       </c>
@@ -65838,7 +65838,7 @@
         <v>1318.4566797929795</v>
       </c>
     </row>
-    <row r="2128" spans="1:12" ht="14.5">
+    <row r="2128" spans="1:12">
       <c r="A2128" s="16">
         <v>21395001</v>
       </c>
@@ -65865,7 +65865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2129" spans="1:12" ht="14.5">
+    <row r="2129" spans="1:12">
       <c r="A2129" s="16">
         <v>21396001</v>
       </c>
@@ -65892,7 +65892,7 @@
         <v>-2063.3249583708371</v>
       </c>
     </row>
-    <row r="2130" spans="1:12" ht="14.5">
+    <row r="2130" spans="1:12">
       <c r="A2130" s="16">
         <v>21396002</v>
       </c>
@@ -65919,7 +65919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2131" spans="1:12" ht="14.5">
+    <row r="2131" spans="1:12">
       <c r="A2131" s="16">
         <v>11412002</v>
       </c>
@@ -65946,7 +65946,7 @@
         <v>5015.8923953645362</v>
       </c>
     </row>
-    <row r="2132" spans="1:12" ht="14.5">
+    <row r="2132" spans="1:12">
       <c r="A2132" s="16">
         <v>95004310</v>
       </c>
@@ -65973,7 +65973,7 @@
         <v>-1318.4566797929763</v>
       </c>
     </row>
-    <row r="2133" spans="1:12" ht="14.5">
+    <row r="2133" spans="1:12">
       <c r="A2133" s="31" t="s">
         <v>1807</v>
       </c>
@@ -66000,7 +66000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2134" spans="1:12" ht="14.5">
+    <row r="2134" spans="1:12">
       <c r="A2134" s="27" t="s">
         <v>1808</v>
       </c>
@@ -66027,7 +66027,7 @@
         <v>-644.2135396039605</v>
       </c>
     </row>
-    <row r="2135" spans="1:12" ht="14.5">
+    <row r="2135" spans="1:12">
       <c r="A2135" s="27" t="s">
         <v>1809</v>
       </c>
@@ -66055,7 +66055,7 @@
         <v>35.925672817281729</v>
       </c>
     </row>
-    <row r="2136" spans="1:12" ht="14.5">
+    <row r="2136" spans="1:12">
       <c r="A2136" s="27" t="s">
         <v>1810</v>
       </c>
@@ -66083,7 +66083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2137" spans="1:12" ht="14.5">
+    <row r="2137" spans="1:12">
       <c r="A2137" s="27" t="s">
         <v>1811</v>
       </c>
@@ -66111,7 +66111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2138" spans="1:12" ht="14.5">
+    <row r="2138" spans="1:12">
       <c r="A2138" s="27" t="s">
         <v>1812</v>
       </c>
@@ -66139,7 +66139,7 @@
         <v>10.215684068406841</v>
       </c>
     </row>
-    <row r="2139" spans="1:12" ht="14.5">
+    <row r="2139" spans="1:12">
       <c r="A2139" s="27" t="s">
         <v>1813</v>
       </c>
@@ -66167,7 +66167,7 @@
         <v>44.553661116111613</v>
       </c>
     </row>
-    <row r="2140" spans="1:12" ht="14.5">
+    <row r="2140" spans="1:12">
       <c r="A2140" s="27" t="s">
         <v>1814</v>
       </c>
@@ -66195,7 +66195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2141" spans="1:12" ht="14.5">
+    <row r="2141" spans="1:12">
       <c r="A2141" s="27" t="s">
         <v>1815</v>
       </c>
@@ -66223,7 +66223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2142" spans="1:12" ht="14.5">
+    <row r="2142" spans="1:12">
       <c r="A2142" s="27" t="s">
         <v>1816</v>
       </c>
@@ -66251,7 +66251,7 @@
         <v>-0.30201057605759474</v>
       </c>
     </row>
-    <row r="2143" spans="1:12" ht="14.5">
+    <row r="2143" spans="1:12">
       <c r="A2143" s="27" t="s">
         <v>1817</v>
       </c>
@@ -66279,7 +66279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2144" spans="1:12" ht="14.5">
+    <row r="2144" spans="1:12">
       <c r="A2144" s="27" t="s">
         <v>1818</v>
       </c>
@@ -66307,7 +66307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2145" spans="1:12" ht="14.5">
+    <row r="2145" spans="1:12">
       <c r="A2145" s="27" t="s">
         <v>1819</v>
       </c>
@@ -66335,7 +66335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2146" spans="1:12" ht="14.5">
+    <row r="2146" spans="1:12">
       <c r="A2146" s="27" t="s">
         <v>1820</v>
       </c>
@@ -66363,7 +66363,7 @@
         <v>660.13266201620161</v>
       </c>
     </row>
-    <row r="2147" spans="1:12" ht="14.5">
+    <row r="2147" spans="1:12">
       <c r="A2147" s="27" t="s">
         <v>1821</v>
       </c>
@@ -66391,7 +66391,7 @@
         <v>1.4075585058505851</v>
       </c>
     </row>
-    <row r="2148" spans="1:12" ht="14.5">
+    <row r="2148" spans="1:12">
       <c r="A2148" s="27" t="s">
         <v>1822</v>
       </c>
@@ -66419,7 +66419,7 @@
         <v>12.676614536453645</v>
       </c>
     </row>
-    <row r="2149" spans="1:12" ht="14.5">
+    <row r="2149" spans="1:12">
       <c r="A2149" s="27" t="s">
         <v>1823</v>
       </c>
@@ -66447,7 +66447,7 @@
         <v>3.0046129612961296</v>
       </c>
     </row>
-    <row r="2150" spans="1:12" ht="14.5">
+    <row r="2150" spans="1:12">
       <c r="A2150" s="27" t="s">
         <v>1824</v>
       </c>
@@ -66475,7 +66475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2151" spans="1:12" ht="14.5">
+    <row r="2151" spans="1:12">
       <c r="A2151" s="27" t="s">
         <v>1825</v>
       </c>
@@ -66502,7 +66502,7 @@
         <v>15071.47952520252</v>
       </c>
     </row>
-    <row r="2152" spans="1:12" ht="14.5">
+    <row r="2152" spans="1:12">
       <c r="A2152" s="27" t="s">
         <v>1826</v>
       </c>
@@ -66530,7 +66530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2153" spans="1:12" ht="14.5">
+    <row r="2153" spans="1:12">
       <c r="A2153" s="27" t="s">
         <v>1827</v>
       </c>
@@ -66558,7 +66558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2154" spans="1:12" ht="14.5">
+    <row r="2154" spans="1:12">
       <c r="A2154" s="31" t="s">
         <v>1828</v>
       </c>
@@ -66585,7 +66585,7 @@
         <v>1578.3192079207922</v>
       </c>
     </row>
-    <row r="2155" spans="1:12" ht="14.5">
+    <row r="2155" spans="1:12">
       <c r="A2155" s="31" t="s">
         <v>1829</v>
       </c>
@@ -66612,7 +66612,7 @@
         <v>62.041455895589557</v>
       </c>
     </row>
-    <row r="2156" spans="1:12" ht="14.5">
+    <row r="2156" spans="1:12">
       <c r="A2156" s="27" t="s">
         <v>1830</v>
       </c>
@@ -66640,7 +66640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2157" spans="1:12" ht="14.5">
+    <row r="2157" spans="1:12">
       <c r="A2157" s="27" t="s">
         <v>1831</v>
       </c>
@@ -66668,7 +66668,7 @@
         <v>4.6223886138613866</v>
       </c>
     </row>
-    <row r="2158" spans="1:12" ht="14.5">
+    <row r="2158" spans="1:12">
       <c r="A2158" s="27" t="s">
         <v>1832</v>
       </c>
@@ -66696,7 +66696,7 @@
         <v>1.6708393339333933</v>
       </c>
     </row>
-    <row r="2159" spans="1:12" ht="14.5">
+    <row r="2159" spans="1:12">
       <c r="A2159" s="27" t="s">
         <v>1833</v>
       </c>
@@ -66724,7 +66724,7 @@
         <v>7.5809045904590464</v>
       </c>
     </row>
-    <row r="2160" spans="1:12" ht="14.5">
+    <row r="2160" spans="1:12">
       <c r="A2160" s="27" t="s">
         <v>1834</v>
       </c>
@@ -66752,7 +66752,7 @@
         <v>3.1490481548154818</v>
       </c>
     </row>
-    <row r="2161" spans="1:12" ht="14.5">
+    <row r="2161" spans="1:12">
       <c r="A2161" s="27" t="s">
         <v>1835</v>
       </c>
@@ -66780,7 +66780,7 @@
         <v>6.4102970297029707</v>
       </c>
     </row>
-    <row r="2162" spans="1:12" ht="14.5">
+    <row r="2162" spans="1:12">
       <c r="A2162" s="27" t="s">
         <v>1836</v>
       </c>
@@ -66808,7 +66808,7 @@
         <v>19.252310981098109</v>
       </c>
     </row>
-    <row r="2163" spans="1:12" ht="14.5">
+    <row r="2163" spans="1:12">
       <c r="A2163" s="27" t="s">
         <v>1837</v>
       </c>
@@ -66836,7 +66836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2164" spans="1:12" ht="14.5">
+    <row r="2164" spans="1:12">
       <c r="A2164" s="27" t="s">
         <v>1838</v>
       </c>
@@ -66864,7 +66864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2165" spans="1:12" ht="14.5">
+    <row r="2165" spans="1:12">
       <c r="A2165" s="27" t="s">
         <v>1839</v>
       </c>
@@ -66892,7 +66892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2166" spans="1:12" ht="14.5">
+    <row r="2166" spans="1:12">
       <c r="A2166" s="27" t="s">
         <v>1840</v>
       </c>
@@ -66920,7 +66920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2167" spans="1:12" ht="14.5">
+    <row r="2167" spans="1:12">
       <c r="A2167" s="27" t="s">
         <v>1841</v>
       </c>
@@ -66948,7 +66948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2168" spans="1:12" ht="14.5">
+    <row r="2168" spans="1:12">
       <c r="A2168" s="27" t="s">
         <v>1842</v>
       </c>
@@ -66976,7 +66976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2169" spans="1:12" ht="14.5">
+    <row r="2169" spans="1:12">
       <c r="A2169" s="27" t="s">
         <v>1843</v>
       </c>
@@ -67004,7 +67004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2170" spans="1:12" ht="14.5">
+    <row r="2170" spans="1:12">
       <c r="A2170" s="27" t="s">
         <v>1844</v>
       </c>
@@ -67032,7 +67032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2171" spans="1:12" ht="14.5">
+    <row r="2171" spans="1:12">
       <c r="A2171" s="27" t="s">
         <v>1845</v>
       </c>
@@ -67060,7 +67060,7 @@
         <v>-0.12373987398739873</v>
       </c>
     </row>
-    <row r="2172" spans="1:12" ht="14.5">
+    <row r="2172" spans="1:12">
       <c r="A2172" s="27" t="s">
         <v>1846</v>
       </c>
@@ -67088,7 +67088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2173" spans="1:12" ht="14.5">
+    <row r="2173" spans="1:12">
       <c r="A2173" s="27" t="s">
         <v>1847</v>
       </c>
@@ -67116,7 +67116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2174" spans="1:12" ht="14.5">
+    <row r="2174" spans="1:12">
       <c r="A2174" s="27" t="s">
         <v>1848</v>
       </c>
@@ -67144,7 +67144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2175" spans="1:12" ht="14.5">
+    <row r="2175" spans="1:12">
       <c r="A2175" s="27" t="s">
         <v>1849</v>
       </c>
@@ -67172,7 +67172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2176" spans="1:12" ht="14.5">
+    <row r="2176" spans="1:12">
       <c r="A2176" s="27" t="s">
         <v>1850</v>
       </c>
@@ -67200,7 +67200,7 @@
         <v>4.3575787578757881</v>
       </c>
     </row>
-    <row r="2177" spans="1:12" ht="14.5">
+    <row r="2177" spans="1:12">
       <c r="A2177" s="27" t="s">
         <v>1851</v>
       </c>
@@ -67228,7 +67228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2178" spans="1:12" ht="14.5">
+    <row r="2178" spans="1:12">
       <c r="A2178" s="27" t="s">
         <v>1852</v>
       </c>
@@ -67256,7 +67256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2179" spans="1:12" ht="14.5">
+    <row r="2179" spans="1:12">
       <c r="A2179" s="27" t="s">
         <v>1853</v>
       </c>
@@ -67284,7 +67284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2180" spans="1:12" ht="14.5">
+    <row r="2180" spans="1:12">
       <c r="A2180" s="27" t="s">
         <v>1854</v>
       </c>
@@ -67312,7 +67312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2181" spans="1:12" ht="14.5">
+    <row r="2181" spans="1:12">
       <c r="A2181" s="27" t="s">
         <v>1855</v>
       </c>
@@ -67340,7 +67340,7 @@
         <v>12.153415841584158</v>
       </c>
     </row>
-    <row r="2182" spans="1:12" ht="14.5">
+    <row r="2182" spans="1:12">
       <c r="A2182" s="27" t="s">
         <v>1856</v>
       </c>
@@ -67368,7 +67368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2183" spans="1:12" ht="14.5">
+    <row r="2183" spans="1:12">
       <c r="A2183" s="27" t="s">
         <v>1857</v>
       </c>
@@ -67396,7 +67396,7 @@
         <v>5.0378757875787574</v>
       </c>
     </row>
-    <row r="2184" spans="1:12" ht="14.5">
+    <row r="2184" spans="1:12">
       <c r="A2184" s="27" t="s">
         <v>1885</v>
       </c>
@@ -67424,7 +67424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2185" spans="1:12" ht="14.5">
+    <row r="2185" spans="1:12">
       <c r="A2185" s="27" t="s">
         <v>1886</v>
       </c>
@@ -67452,7 +67452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2186" spans="1:12" ht="14.5">
+    <row r="2186" spans="1:12">
       <c r="A2186" s="27" t="s">
         <v>1858</v>
       </c>
@@ -67480,7 +67480,7 @@
         <v>33.812610261026101</v>
       </c>
     </row>
-    <row r="2187" spans="1:12" ht="14.5">
+    <row r="2187" spans="1:12">
       <c r="A2187" s="27" t="s">
         <v>1859</v>
       </c>
@@ -67508,7 +67508,7 @@
         <v>15.454376687668766</v>
       </c>
     </row>
-    <row r="2188" spans="1:12" ht="14.5">
+    <row r="2188" spans="1:12">
       <c r="A2188" s="27" t="s">
         <v>1860</v>
       </c>
@@ -67536,7 +67536,7 @@
         <v>6.1481716921692167</v>
       </c>
     </row>
-    <row r="2189" spans="1:12" ht="14.5">
+    <row r="2189" spans="1:12">
       <c r="A2189" s="27" t="s">
         <v>1861</v>
       </c>
@@ -67564,7 +67564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2190" spans="1:12" ht="14.5">
+    <row r="2190" spans="1:12">
       <c r="A2190" s="27" t="s">
         <v>1862</v>
       </c>
@@ -67592,7 +67592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2191" spans="1:12" ht="14.5">
+    <row r="2191" spans="1:12">
       <c r="A2191" s="27" t="s">
         <v>1863</v>
       </c>
@@ -67620,7 +67620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2192" spans="1:12" ht="14.5">
+    <row r="2192" spans="1:12">
       <c r="A2192" s="27" t="s">
         <v>1864</v>
       </c>
@@ -67648,7 +67648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2193" spans="1:12" ht="14.5">
+    <row r="2193" spans="1:12">
       <c r="A2193" s="27" t="s">
         <v>1865</v>
       </c>
@@ -67676,7 +67676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2194" spans="1:12" ht="14.5">
+    <row r="2194" spans="1:12">
       <c r="A2194" s="27" t="s">
         <v>1866</v>
       </c>
@@ -67704,7 +67704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2195" spans="1:12" ht="14.5">
+    <row r="2195" spans="1:12">
       <c r="A2195" s="33" t="s">
         <v>1867</v>
       </c>
@@ -67731,7 +67731,7 @@
         <v>-2432.394641089109</v>
       </c>
     </row>
-    <row r="2196" spans="1:12" ht="14.5">
+    <row r="2196" spans="1:12">
       <c r="A2196" s="33" t="s">
         <v>1868</v>
       </c>
@@ -67866,7 +67866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2201" spans="1:12" ht="14.5">
+    <row r="2201" spans="1:12">
       <c r="A2201" s="33" t="s">
         <v>1873</v>
       </c>
@@ -67920,7 +67920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2203" spans="1:12" ht="14.5">
+    <row r="2203" spans="1:12">
       <c r="A2203" s="33" t="s">
         <v>1875</v>
       </c>
@@ -68052,37 +68052,37 @@
     <cfRule type="duplicateValues" dxfId="29" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="28" priority="188"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="188"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C2204">
-    <cfRule type="duplicateValues" dxfId="26" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="175"/>
     <cfRule type="duplicateValues" dxfId="25" priority="174"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C137">
     <cfRule type="duplicateValues" dxfId="23" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C138:C155 C157:C2016 C2:C136">
     <cfRule type="duplicateValues" dxfId="22" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C156">
     <cfRule type="duplicateValues" dxfId="19" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2018:C2196">
-    <cfRule type="duplicateValues" dxfId="18" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="169"/>
     <cfRule type="duplicateValues" dxfId="17" priority="168"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2197">
     <cfRule type="duplicateValues" dxfId="15" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2199">
-    <cfRule type="duplicateValues" dxfId="14" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="51"/>
     <cfRule type="duplicateValues" dxfId="13" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2201">
     <cfRule type="duplicateValues" dxfId="11" priority="30"/>
@@ -68097,8 +68097,8 @@
     <cfRule type="duplicateValues" dxfId="6" priority="187"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2205:E2205">
-    <cfRule type="duplicateValues" dxfId="5" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="57"/>
     <cfRule type="duplicateValues" dxfId="3" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2201">
